--- a/Dataset/2_label/OPENING-CLOSING_OPENING-CLOSING_V1_5 divisions_per_second.xlsx
+++ b/Dataset/2_label/OPENING-CLOSING_OPENING-CLOSING_V1_5 divisions_per_second.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2664,6 +2664,114 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V1_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>26800</v>
+      </c>
+      <c r="C125" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V1_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>27000</v>
+      </c>
+      <c r="C126" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V1_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>27200</v>
+      </c>
+      <c r="C127" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V1_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>27400</v>
+      </c>
+      <c r="C128" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V1_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>27600</v>
+      </c>
+      <c r="C129" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V1_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>27800</v>
+      </c>
+      <c r="C130" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
